--- a/product_selector_out/STM32WB series.xlsx
+++ b/product_selector_out/STM32WB series.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9401,14 +9401,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -9491,9 +9491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9855,14 +9855,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9980,9 +9980,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -10025,9 +10025,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -10085,14 +10085,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -10175,9 +10175,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10197,14 +10197,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10322,9 +10322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -10367,9 +10367,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -10427,14 +10427,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -10517,9 +10517,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10539,14 +10539,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10664,9 +10664,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -10709,9 +10709,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -10769,14 +10769,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10859,9 +10859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10881,14 +10881,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -11006,9 +11006,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -11051,9 +11051,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -11111,14 +11111,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -11201,9 +11201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11565,14 +11565,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11690,9 +11690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD23" s="6" t="inlineStr">
@@ -11735,9 +11735,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -11795,14 +11795,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11885,9 +11885,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11907,14 +11907,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -12032,9 +12032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -12077,9 +12077,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -12137,14 +12137,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12249,14 +12249,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12374,9 +12374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD25" s="6" t="inlineStr">
@@ -12419,9 +12419,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="6" t="inlineStr">
@@ -12479,14 +12479,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12591,14 +12591,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12716,9 +12716,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD26" s="6" t="inlineStr">
@@ -12761,9 +12761,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM26" s="6" t="inlineStr">
@@ -12821,14 +12821,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12911,9 +12911,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12933,14 +12933,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -13058,9 +13058,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -13103,9 +13103,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr">
@@ -13163,14 +13163,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -13253,9 +13253,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13275,14 +13275,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13400,9 +13400,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD28" s="8" t="inlineStr">
@@ -13445,9 +13445,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM28" s="6" t="inlineStr">
@@ -13505,14 +13505,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -13595,9 +13595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13617,14 +13617,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13742,9 +13742,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD29" s="6" t="inlineStr">
@@ -13787,9 +13787,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="6" t="inlineStr">
@@ -13847,14 +13847,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -13937,9 +13937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14073,14 +14073,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WB30CE</t>
+          <t>STM32WB15CC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14095,19 +14095,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WB15CC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14117,19 +14117,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the footnote qualifies the figure</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14139,513 +14139,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WB series.xlsx
+++ b/product_selector_out/STM32WB series.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9401,14 +9401,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -9491,9 +9491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9855,14 +9855,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9980,9 +9980,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC18" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -10025,9 +10025,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL18" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -10085,14 +10085,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -10175,9 +10175,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10197,14 +10197,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10322,9 +10322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC19" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -10367,9 +10367,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL19" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -10427,14 +10427,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -10517,9 +10517,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10539,14 +10539,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10664,9 +10664,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -10709,9 +10709,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -10769,14 +10769,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10859,9 +10859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10881,14 +10881,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -11006,9 +11006,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -11051,9 +11051,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -11111,14 +11111,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -11201,9 +11201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11565,14 +11565,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11690,9 +11690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD23" s="6" t="inlineStr">
@@ -11735,9 +11735,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -11795,14 +11795,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11885,9 +11885,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11907,14 +11907,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -12032,9 +12032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -12077,9 +12077,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -12137,14 +12137,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12249,14 +12249,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12374,9 +12374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD25" s="6" t="inlineStr">
@@ -12419,9 +12419,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM25" s="6" t="inlineStr">
@@ -12479,14 +12479,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12591,14 +12591,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12716,9 +12716,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD26" s="6" t="inlineStr">
@@ -12761,9 +12761,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM26" s="6" t="inlineStr">
@@ -12821,14 +12821,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX26" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12911,9 +12911,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12933,14 +12933,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -13058,9 +13058,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC27" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -13103,9 +13103,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL27" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr">
@@ -13163,14 +13163,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX27" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY27" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -13253,9 +13253,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13275,14 +13275,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13400,9 +13400,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC28" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD28" s="8" t="inlineStr">
@@ -13445,9 +13445,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL28" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM28" s="6" t="inlineStr">
@@ -13505,14 +13505,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY28" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -13595,9 +13595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13617,14 +13617,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13742,9 +13742,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC29" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD29" s="6" t="inlineStr">
@@ -13787,9 +13787,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL29" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM29" s="6" t="inlineStr">
@@ -13847,14 +13847,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY29" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -13937,9 +13937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14080,7 +14080,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WB15CC</t>
+          <t>STM32WB30CE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14095,19 +14095,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB15CC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14117,27 +14117,533 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>STM32WB55RC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WB55RC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>STM32WB55CC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32WB55CC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WB series.xlsx
+++ b/product_selector_out/STM32WB series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4178,7 +4184,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -5204,7 +5210,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -9925,14 +9931,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -10267,14 +10273,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -10609,14 +10615,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10951,14 +10957,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -11293,14 +11299,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -11635,14 +11641,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11977,14 +11983,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12319,14 +12325,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -12661,14 +12667,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -13003,14 +13009,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -13345,14 +13351,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13687,14 +13693,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">

--- a/product_selector_out/STM32WB series.xlsx
+++ b/product_selector_out/STM32WB series.xlsx
@@ -2724,7 +2724,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9182,9 +9182,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9407,14 +9407,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -9497,9 +9497,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9861,14 +9861,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9931,14 +9931,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -9986,9 +9986,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -10031,9 +10031,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -10091,14 +10091,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -10181,9 +10181,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10203,14 +10203,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10273,14 +10273,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -10328,9 +10328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -10373,9 +10373,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -10433,14 +10433,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -10523,9 +10523,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10545,14 +10545,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10615,14 +10615,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10670,9 +10670,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -10715,9 +10715,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -10775,14 +10775,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10865,9 +10865,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10887,14 +10887,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10957,14 +10957,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -11012,9 +11012,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -11057,9 +11057,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -11117,14 +11117,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -11207,9 +11207,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11571,14 +11571,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11641,14 +11641,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11696,9 +11696,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD23" s="6" t="inlineStr">
@@ -11741,9 +11741,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -11801,14 +11801,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11891,9 +11891,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11913,14 +11913,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11983,14 +11983,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12038,9 +12038,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -12083,9 +12083,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -12143,14 +12143,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -12233,9 +12233,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12255,14 +12255,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12325,14 +12325,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -12380,9 +12380,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD25" s="6" t="inlineStr">
@@ -12425,9 +12425,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="6" t="inlineStr">
@@ -12485,14 +12485,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -12575,9 +12575,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12597,14 +12597,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12667,14 +12667,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R26" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12722,9 +12722,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD26" s="6" t="inlineStr">
@@ -12767,9 +12767,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM26" s="6" t="inlineStr">
@@ -12827,14 +12827,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12917,9 +12917,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12939,14 +12939,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -13009,14 +13009,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R27" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -13064,9 +13064,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD27" s="8" t="inlineStr">
@@ -13109,9 +13109,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr">
@@ -13169,14 +13169,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -13259,9 +13259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13281,14 +13281,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13351,14 +13351,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13406,9 +13406,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD28" s="8" t="inlineStr">
@@ -13451,9 +13451,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM28" s="6" t="inlineStr">
@@ -13511,14 +13511,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -13601,9 +13601,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13623,14 +13623,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13693,14 +13693,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R29" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -13748,9 +13748,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD29" s="6" t="inlineStr">
@@ -13793,9 +13793,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="6" t="inlineStr">
@@ -13853,14 +13853,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -13943,9 +13943,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14086,7 +14086,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WB30CE</t>
+          <t>STM32WB15CC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14101,19 +14101,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WB15CC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14123,19 +14123,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14144,512 +14144,6 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WB series.xlsx
+++ b/product_selector_out/STM32WB series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BQ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.875" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -919,6 +920,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1017,6 +1023,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1356,6 +1363,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb1mmc.pdf</t>
         </is>
       </c>
@@ -1698,6 +1710,11 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb5mmg.pdf</t>
         </is>
       </c>
@@ -2040,6 +2057,11 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb10cc.pdf</t>
         </is>
       </c>
@@ -2382,6 +2404,11 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
         </is>
       </c>
@@ -2727,6 +2754,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3066,6 +3098,11 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb15cc.pdf</t>
         </is>
       </c>
@@ -3411,6 +3448,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3753,6 +3795,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4095,6 +4142,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4437,6 +4489,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4776,6 +4833,11 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
@@ -5121,6 +5183,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5463,6 +5530,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5805,6 +5877,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6147,6 +6224,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6489,6 +6571,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6831,6 +6918,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7173,9 +7265,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7198,14 +7295,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7223,6 +7319,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -7235,6 +7332,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -7275,7 +7373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BQ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7346,6 +7444,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7694,6 +7793,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7792,6 +7896,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8129,7 +8234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8471,7 +8581,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8813,7 +8928,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9155,7 +9275,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9502,6 +9627,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9839,7 +9969,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10186,6 +10321,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -10528,6 +10668,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -10870,6 +11015,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -11212,6 +11362,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11549,7 +11704,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
+      <c r="BP22" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BQ22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11896,6 +12056,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -12238,6 +12403,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12580,6 +12750,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -12922,6 +13097,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -13264,6 +13444,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13606,6 +13791,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -13948,11 +14138,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
